--- a/Взаимодействие компонент.xlsx
+++ b/Взаимодействие компонент.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25800" windowHeight="11320"/>
+    <workbookView windowWidth="25600" windowHeight="10400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="23">
   <si>
     <t>Есть 4 геометрические зоны, два сорта пикапов и 9 сортов водорода</t>
   </si>
@@ -94,6 +94,9 @@
   <si>
     <t>Таблица взаимодействия из статьи Бера</t>
   </si>
+  <si>
+    <t>Зона 3-4</t>
+  </si>
 </sst>
 </file>
 
@@ -105,7 +108,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,13 +151,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -740,148 +736,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1271,7 +1267,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" ht="15.25" spans="1:1">
@@ -2428,143 +2424,110 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" ht="18.5" spans="1:1">
-      <c r="A71" s="26" t="s">
+    <row r="70" ht="15.25"/>
+    <row r="71" spans="1:4">
+      <c r="A71" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="24"/>
-      <c r="B73" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H73" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G74" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="H74" s="27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="H75" s="27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G76" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H76" s="25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="25"/>
-    </row>
-    <row r="79" ht="18.5" spans="1:1">
-      <c r="A79" s="26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="24"/>
-      <c r="B81" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" s="24"/>
-      <c r="G81" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="24" t="s">
-        <v>6</v>
+      <c r="D71" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="12"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="14"/>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="15"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="18"/>
+    </row>
+    <row r="77" ht="15.25" spans="1:4">
+      <c r="A77" s="19"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="22"/>
+    </row>
+    <row r="80" ht="18.5" spans="1:1">
+      <c r="A80" s="26" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G82" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H82" s="25" t="s">
-        <v>5</v>
+      <c r="A82" s="24"/>
+      <c r="B82" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F82" s="24"/>
+      <c r="G82" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H82" s="24" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G83" s="25" t="s">
         <v>5</v>
@@ -2575,23 +2538,192 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="24" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G84" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H84" s="25" t="s">
-        <v>5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G84" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H84" s="27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G85" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H85" s="27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="25"/>
+    </row>
+    <row r="88" ht="18.5" spans="1:1">
+      <c r="A88" s="26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="24"/>
+      <c r="B90" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F90" s="24"/>
+      <c r="G90" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H90" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G91" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H92" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G93" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H93" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" ht="18.5" spans="1:1">
+      <c r="A96" s="26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="24"/>
+      <c r="B98" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H98" s="24"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="25"/>
+      <c r="F99" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H99" s="25"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="25"/>
+      <c r="F100" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="25"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="25"/>
+      <c r="F101" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G101" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
